--- a/apps/configurador-servicios/catalog/Catalogo_Tecnico_Servicios_ISM_Developer_v2_1_Auditado.xlsx
+++ b/apps/configurador-servicios/catalog/Catalogo_Tecnico_Servicios_ISM_Developer_v2_1_Auditado.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" r:id="Rb8b1f89a6d554b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="2" r:id="Rec0d74e02fd44480"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" r:id="R7cce6742963f494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo Maestro" sheetId="4" r:id="R9492d02b7ef94edd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desarrollo" sheetId="5" r:id="R2de89e65c9924d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento" sheetId="6" r:id="R9bae3565644d4eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoreo" sheetId="7" r:id="R4ed3d8ca78e94a98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuidad" sheetId="8" r:id="R7f04be02b8a64cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ciberseguridad" sheetId="9" r:id="R3007ded1d7b34d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soporte" sheetId="10" r:id="Re41223fd3ad6453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion HH" sheetId="11" r:id="R2ec1213a806d43c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionarios" sheetId="12" r:id="R0e028dba1dfe4ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control redundancias" sheetId="13" r:id="R106e1e40284544e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" r:id="R33eb17d39c4240be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="2" r:id="Rfefe9e4b022a4f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" r:id="R918c0bf5be3f4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo Maestro" sheetId="4" r:id="R7f7a548bf2b9414c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desarrollo" sheetId="5" r:id="R99b3f0f59e1e43d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mantenimiento" sheetId="6" r:id="R98006b58727e4869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoreo" sheetId="7" r:id="R792349f95e5d4d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuidad" sheetId="8" r:id="R50d0bc8a4fdf4c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ciberseguridad" sheetId="9" r:id="Rad1a285a24eb463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Soporte" sheetId="10" r:id="R0b75c68ba261424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validacion HH" sheetId="11" r:id="R803dfd25dd30494c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionarios" sheetId="12" r:id="R62c00dddaf134d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control redundancias" sheetId="13" r:id="Rd5e064754d7f4224"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1105,7 +1105,7 @@
         <x:color rgb="FF14532D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDF5E7"/>
         </x:patternFill>
       </x:fill>
@@ -1116,7 +1116,7 @@
         <x:color rgb="FF7C4A03"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -1267,7 +1267,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5eff4cbfa2374e5f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R874fa5ade7e34202"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6170,7 +6170,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b3060335a6e4b03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R807c68ac26714d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7179,7 +7179,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R627ce11d2e734add"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55402056370e42eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8351,7 +8351,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd28496b88f441c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43beb5db784d4725"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8901,19 +8901,19 @@
       </x:c>
       <x:c r="D8" s="67" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$A$6:$A$287,A8,'Catalogo Maestro'!$T$6:$T$287)</x:f>
-        <x:v>143.66250000000002</x:v>
+        <x:v>147.93125000000003</x:v>
       </x:c>
       <x:c r="E8" s="67" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$A$6:$A$287,A8,'Catalogo Maestro'!$U$6:$U$287)</x:f>
-        <x:v>201.09</x:v>
+        <x:v>207.89656250000002</x:v>
       </x:c>
       <x:c r="F8" s="67" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$A$6:$A$287,A8,'Catalogo Maestro'!$V$6:$V$287)</x:f>
-        <x:v>246.55812499999996</x:v>
+        <x:v>255.26999999999998</x:v>
       </x:c>
       <x:c r="G8" s="67" t="n">
         <x:f>E8*(1+Parametros!$B$9)</x:f>
-        <x:v>241.308</x:v>
+        <x:v>249.475875</x:v>
       </x:c>
       <x:c r="H8" s="67" t="n">
         <x:f>COUNTIFS('Catalogo Maestro'!$A$6:$A$287,A8,'Catalogo Maestro'!$AA$6:$AA$287,"Validado con proyecto")+COUNTIFS('Catalogo Maestro'!$A$6:$A$287,A8,'Catalogo Maestro'!$AA$6:$AA$287,"Aprobado")</x:f>
@@ -9129,19 +9129,19 @@
       </x:c>
       <x:c r="D14" s="139" t="n">
         <x:f>SUM(D8:D13)</x:f>
-        <x:v>578.7099999999999</x:v>
+        <x:v>582.97875</x:v>
       </x:c>
       <x:c r="E14" s="139" t="n">
         <x:f>SUM(E8:E13)</x:f>
-        <x:v>808.478875</x:v>
+        <x:v>815.2854375</x:v>
       </x:c>
       <x:c r="F14" s="139" t="n">
         <x:f>SUM(F8:F13)</x:f>
-        <x:v>990.5936250000001</x:v>
+        <x:v>999.3055</x:v>
       </x:c>
       <x:c r="G14" s="139" t="n">
         <x:f>SUM(G8:G13)</x:f>
-        <x:v>970.1746499999999</x:v>
+        <x:v>978.3425249999999</x:v>
       </x:c>
       <x:c r="H14" s="139" t="n">
         <x:f>SUM(H8:H13)</x:f>
@@ -9219,19 +9219,19 @@
       </x:c>
       <x:c r="F20" s="67" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$B$6:$B$287,B20,'Catalogo Maestro'!$T$6:$T$287)</x:f>
-        <x:v>31.7625</x:v>
+        <x:v>30.231250000000003</x:v>
       </x:c>
       <x:c r="G20" s="67" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$B$6:$B$287,B20,'Catalogo Maestro'!$U$6:$U$287)</x:f>
-        <x:v>41.81249999999999</x:v>
+        <x:v>40.074062500000004</x:v>
       </x:c>
       <x:c r="H20" s="67" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$B$6:$B$287,B20,'Catalogo Maestro'!$V$6:$V$287)</x:f>
-        <x:v>50.10062500000001</x:v>
+        <x:v>48.1475</x:v>
       </x:c>
       <x:c r="I20" s="67" t="n">
         <x:f>G20*(1+Parametros!$B$9)</x:f>
-        <x:v>50.17499999999999</x:v>
+        <x:v>48.088875</x:v>
       </x:c>
       <x:c r="J20" s="38" t="str">
         <x:v>Preliminar</x:v>
@@ -9255,19 +9255,19 @@
       </x:c>
       <x:c r="F21" s="68" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$B$6:$B$287,B21,'Catalogo Maestro'!$T$6:$T$287)</x:f>
-        <x:v>80.625</x:v>
+        <x:v>86.42500000000001</x:v>
       </x:c>
       <x:c r="G21" s="68" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$B$6:$B$287,B21,'Catalogo Maestro'!$U$6:$U$287)</x:f>
-        <x:v>114.96374999999999</x:v>
+        <x:v>123.50875</x:v>
       </x:c>
       <x:c r="H21" s="68" t="n">
         <x:f>SUMIF('Catalogo Maestro'!$B$6:$B$287,B21,'Catalogo Maestro'!$V$6:$V$287)</x:f>
-        <x:v>141.88750000000005</x:v>
+        <x:v>152.5525</x:v>
       </x:c>
       <x:c r="I21" s="68" t="n">
         <x:f>G21*(1+Parametros!$B$9)</x:f>
-        <x:v>137.95649999999998</x:v>
+        <x:v>148.2105</x:v>
       </x:c>
       <x:c r="J21" s="41" t="str">
         <x:v>Preliminar</x:v>
@@ -9969,10 +9969,10 @@
     <x:mergeCell ref="A18:J18"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f65626c082b40c8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01949ccacb214167"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02a0fd47ee7a45ed"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0b349e99f94e32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a178478fc1f4486"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb716025250c146c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10567,7 +10567,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I10" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J10" s="73" t="str">
         <x:v>Sí</x:v>
@@ -10602,15 +10602,15 @@
       </x:c>
       <x:c r="T10" s="85" t="n">
         <x:f>IF(J10="Sí",I10*O10*Q10,0)</x:f>
-        <x:v>0.55</x:v>
+        <x:v>0.275</x:v>
       </x:c>
       <x:c r="U10" s="85" t="n">
         <x:f>IF(J10="Sí",I10*O10*R10,0)</x:f>
-        <x:v>0.6325</x:v>
+        <x:v>0.31625</x:v>
       </x:c>
       <x:c r="V10" s="85" t="n">
         <x:f>IF(J10="Sí",I10*O10*S10,0)</x:f>
-        <x:v>0.7150000000000001</x:v>
+        <x:v>0.35750000000000004</x:v>
       </x:c>
       <x:c r="W10" s="73"/>
       <x:c r="X10" s="73" t="str">
@@ -10915,7 +10915,7 @@
         <x:v>Sección</x:v>
       </x:c>
       <x:c r="I14" s="85" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J14" s="73" t="str">
         <x:v>Sí</x:v>
@@ -10950,15 +10950,15 @@
       </x:c>
       <x:c r="T14" s="85" t="n">
         <x:f>IF(J14="Sí",I14*O14*Q14,0)</x:f>
-        <x:v>3</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="U14" s="85" t="n">
         <x:f>IF(J14="Sí",I14*O14*R14,0)</x:f>
-        <x:v>3.9000000000000004</x:v>
+        <x:v>0.9750000000000001</x:v>
       </x:c>
       <x:c r="V14" s="85" t="n">
         <x:f>IF(J14="Sí",I14*O14*S14,0)</x:f>
-        <x:v>4.65</x:v>
+        <x:v>1.1625</x:v>
       </x:c>
       <x:c r="W14" s="73"/>
       <x:c r="X14" s="73" t="str">
@@ -11525,7 +11525,7 @@
         <x:v>Página</x:v>
       </x:c>
       <x:c r="I21" s="85" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J21" s="73" t="str">
         <x:v>No</x:v>
@@ -12047,7 +12047,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I27" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J27" s="73" t="str">
         <x:v>Sí</x:v>
@@ -12082,15 +12082,15 @@
       </x:c>
       <x:c r="T27" s="85" t="n">
         <x:f>IF(J27="Sí",I27*O27*Q27,0)</x:f>
-        <x:v>2.4000000000000004</x:v>
+        <x:v>3.6000000000000005</x:v>
       </x:c>
       <x:c r="U27" s="85" t="n">
         <x:f>IF(J27="Sí",I27*O27*R27,0)</x:f>
-        <x:v>3.4800000000000004</x:v>
+        <x:v>5.220000000000001</x:v>
       </x:c>
       <x:c r="V27" s="85" t="n">
         <x:f>IF(J27="Sí",I27*O27*S27,0)</x:f>
-        <x:v>4.320000000000001</x:v>
+        <x:v>6.480000000000001</x:v>
       </x:c>
       <x:c r="W27" s="73" t="str">
         <x:v>WEB-007, WEB-008, WEB-009, WEB-010, WEB-014, WEB-015 y actividades visuales seleccionadas</x:v>
@@ -12225,7 +12225,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I29" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J29" s="73" t="str">
         <x:v>Sí</x:v>
@@ -12260,15 +12260,15 @@
       </x:c>
       <x:c r="T29" s="85" t="n">
         <x:f>IF(J29="Sí",I29*O29*Q29,0)</x:f>
-        <x:v>0.41250000000000003</x:v>
+        <x:v>0.20625000000000002</x:v>
       </x:c>
       <x:c r="U29" s="85" t="n">
         <x:f>IF(J29="Sí",I29*O29*R29,0)</x:f>
-        <x:v>0.474375</x:v>
+        <x:v>0.2371875</x:v>
       </x:c>
       <x:c r="V29" s="85" t="n">
         <x:f>IF(J29="Sí",I29*O29*S29,0)</x:f>
-        <x:v>0.5362500000000001</x:v>
+        <x:v>0.26812500000000006</x:v>
       </x:c>
       <x:c r="W29" s="73"/>
       <x:c r="X29" s="73" t="str">
@@ -13357,7 +13357,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I42" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J42" s="73" t="str">
         <x:v>Sí</x:v>
@@ -13392,15 +13392,15 @@
       </x:c>
       <x:c r="T42" s="85" t="n">
         <x:f>IF(J42="Sí",I42*O42*Q42,0)</x:f>
-        <x:v>2.975</x:v>
+        <x:v>4.4625</x:v>
       </x:c>
       <x:c r="U42" s="85" t="n">
         <x:f>IF(J42="Sí",I42*O42*R42,0)</x:f>
-        <x:v>4.31375</x:v>
+        <x:v>6.470625</x:v>
       </x:c>
       <x:c r="V42" s="85" t="n">
         <x:f>IF(J42="Sí",I42*O42*S42,0)</x:f>
-        <x:v>5.355</x:v>
+        <x:v>8.0325</x:v>
       </x:c>
       <x:c r="W42" s="73" t="str">
         <x:v>APP-002</x:v>
@@ -13445,7 +13445,7 @@
         <x:v>Rol</x:v>
       </x:c>
       <x:c r="I43" s="85" t="n">
-        <x:v>2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J43" s="73" t="str">
         <x:v>Sí</x:v>
@@ -13480,15 +13480,15 @@
       </x:c>
       <x:c r="T43" s="85" t="n">
         <x:f>IF(J43="Sí",I43*O43*Q43,0)</x:f>
-        <x:v>2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="U43" s="85" t="n">
         <x:f>IF(J43="Sí",I43*O43*R43,0)</x:f>
-        <x:v>2.9</x:v>
+        <x:v>2.175</x:v>
       </x:c>
       <x:c r="V43" s="85" t="n">
         <x:f>IF(J43="Sí",I43*O43*S43,0)</x:f>
-        <x:v>3.6</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="W43" s="73" t="str">
         <x:v>APP-002</x:v>
@@ -13533,7 +13533,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I44" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J44" s="73" t="str">
         <x:v>Sí</x:v>
@@ -13568,15 +13568,15 @@
       </x:c>
       <x:c r="T44" s="85" t="n">
         <x:f>IF(J44="Sí",I44*O44*Q44,0)</x:f>
-        <x:v>2.125</x:v>
+        <x:v>3.1875</x:v>
       </x:c>
       <x:c r="U44" s="85" t="n">
         <x:f>IF(J44="Sí",I44*O44*R44,0)</x:f>
-        <x:v>3.08125</x:v>
+        <x:v>4.621875</x:v>
       </x:c>
       <x:c r="V44" s="85" t="n">
         <x:f>IF(J44="Sí",I44*O44*S44,0)</x:f>
-        <x:v>3.825</x:v>
+        <x:v>5.7375</x:v>
       </x:c>
       <x:c r="W44" s="73" t="str">
         <x:v>APP-002</x:v>
@@ -13621,7 +13621,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I45" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J45" s="73" t="str">
         <x:v>Sí</x:v>
@@ -13656,15 +13656,15 @@
       </x:c>
       <x:c r="T45" s="85" t="n">
         <x:f>IF(J45="Sí",I45*O45*Q45,0)</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="U45" s="85" t="n">
         <x:f>IF(J45="Sí",I45*O45*R45,0)</x:f>
-        <x:v>2.9</x:v>
+        <x:v>4.35</x:v>
       </x:c>
       <x:c r="V45" s="85" t="n">
         <x:f>IF(J45="Sí",I45*O45*S45,0)</x:f>
-        <x:v>3.6</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="W45" s="73" t="str">
         <x:v>APP-002</x:v>
@@ -13711,7 +13711,7 @@
         <x:v>Pantalla</x:v>
       </x:c>
       <x:c r="I46" s="85" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J46" s="73" t="str">
         <x:v>Sí</x:v>
@@ -13746,15 +13746,15 @@
       </x:c>
       <x:c r="T46" s="85" t="n">
         <x:f>IF(J46="Sí",I46*O46*Q46,0)</x:f>
-        <x:v>3.75</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="U46" s="85" t="n">
         <x:f>IF(J46="Sí",I46*O46*R46,0)</x:f>
-        <x:v>4.875</x:v>
+        <x:v>2.9250000000000003</x:v>
       </x:c>
       <x:c r="V46" s="85" t="n">
         <x:f>IF(J46="Sí",I46*O46*S46,0)</x:f>
-        <x:v>5.8125</x:v>
+        <x:v>3.4875000000000003</x:v>
       </x:c>
       <x:c r="W46" s="73" t="str">
         <x:v>APP-006</x:v>
@@ -13799,7 +13799,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I47" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J47" s="73" t="str">
         <x:v>Sí</x:v>
@@ -13834,15 +13834,15 @@
       </x:c>
       <x:c r="T47" s="85" t="n">
         <x:f>IF(J47="Sí",I47*O47*Q47,0)</x:f>
-        <x:v>1.2</x:v>
+        <x:v>1.7999999999999998</x:v>
       </x:c>
       <x:c r="U47" s="85" t="n">
         <x:f>IF(J47="Sí",I47*O47*R47,0)</x:f>
-        <x:v>1.56</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="V47" s="85" t="n">
         <x:f>IF(J47="Sí",I47*O47*S47,0)</x:f>
-        <x:v>1.8599999999999999</x:v>
+        <x:v>2.7899999999999996</x:v>
       </x:c>
       <x:c r="W47" s="73" t="str">
         <x:v>APP-005</x:v>
@@ -13887,7 +13887,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I48" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J48" s="73" t="str">
         <x:v>Sí</x:v>
@@ -13922,15 +13922,15 @@
       </x:c>
       <x:c r="T48" s="85" t="n">
         <x:f>IF(J48="Sí",I48*O48*Q48,0)</x:f>
-        <x:v>2.6</x:v>
+        <x:v>3.9000000000000004</x:v>
       </x:c>
       <x:c r="U48" s="85" t="n">
         <x:f>IF(J48="Sí",I48*O48*R48,0)</x:f>
-        <x:v>3.77</x:v>
+        <x:v>5.655</x:v>
       </x:c>
       <x:c r="V48" s="85" t="n">
         <x:f>IF(J48="Sí",I48*O48*S48,0)</x:f>
-        <x:v>4.680000000000001</x:v>
+        <x:v>7.0200000000000005</x:v>
       </x:c>
       <x:c r="W48" s="73" t="str">
         <x:v>APP-006</x:v>
@@ -14067,7 +14067,7 @@
         <x:v>Dashboard</x:v>
       </x:c>
       <x:c r="I50" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J50" s="73" t="str">
         <x:v>No</x:v>
@@ -14157,7 +14157,7 @@
         <x:v>Proyecto</x:v>
       </x:c>
       <x:c r="I51" s="85" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J51" s="73" t="str">
         <x:v>Sí</x:v>
@@ -14192,15 +14192,15 @@
       </x:c>
       <x:c r="T51" s="85" t="n">
         <x:f>IF(J51="Sí",I51*O51*Q51,0)</x:f>
-        <x:v>2.8000000000000003</x:v>
+        <x:v>8.4</x:v>
       </x:c>
       <x:c r="U51" s="85" t="n">
         <x:f>IF(J51="Sí",I51*O51*R51,0)</x:f>
-        <x:v>4.0600000000000005</x:v>
+        <x:v>12.18</x:v>
       </x:c>
       <x:c r="V51" s="85" t="n">
         <x:f>IF(J51="Sí",I51*O51*S51,0)</x:f>
-        <x:v>5.040000000000001</x:v>
+        <x:v>15.120000000000001</x:v>
       </x:c>
       <x:c r="W51" s="73" t="str">
         <x:v>APP-003</x:v>
@@ -14245,7 +14245,7 @@
         <x:v>Entidad</x:v>
       </x:c>
       <x:c r="I52" s="85" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J52" s="73" t="str">
         <x:v>Sí</x:v>
@@ -14280,15 +14280,15 @@
       </x:c>
       <x:c r="T52" s="85" t="n">
         <x:f>IF(J52="Sí",I52*O52*Q52,0)</x:f>
-        <x:v>7.200000000000001</x:v>
+        <x:v>4.800000000000001</x:v>
       </x:c>
       <x:c r="U52" s="85" t="n">
         <x:f>IF(J52="Sí",I52*O52*R52,0)</x:f>
-        <x:v>10.440000000000001</x:v>
+        <x:v>6.960000000000001</x:v>
       </x:c>
       <x:c r="V52" s="85" t="n">
         <x:f>IF(J52="Sí",I52*O52*S52,0)</x:f>
-        <x:v>12.960000000000003</x:v>
+        <x:v>8.640000000000002</x:v>
       </x:c>
       <x:c r="W52" s="73" t="str">
         <x:v>APP-012</x:v>
@@ -14423,7 +14423,7 @@
         <x:v>Rol</x:v>
       </x:c>
       <x:c r="I54" s="85" t="n">
-        <x:v>2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="J54" s="73" t="str">
         <x:v>Sí</x:v>
@@ -14458,15 +14458,15 @@
       </x:c>
       <x:c r="T54" s="85" t="n">
         <x:f>IF(J54="Sí",I54*O54*Q54,0)</x:f>
-        <x:v>3.4</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="U54" s="85" t="n">
         <x:f>IF(J54="Sí",I54*O54*R54,0)</x:f>
-        <x:v>4.93</x:v>
+        <x:v>3.6975</x:v>
       </x:c>
       <x:c r="V54" s="85" t="n">
         <x:f>IF(J54="Sí",I54*O54*S54,0)</x:f>
-        <x:v>6.12</x:v>
+        <x:v>4.59</x:v>
       </x:c>
       <x:c r="W54" s="73" t="str">
         <x:v>APP-004; APP-014</x:v>
@@ -15131,7 +15131,7 @@
         <x:v>Lote</x:v>
       </x:c>
       <x:c r="I62" s="85" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J62" s="73" t="str">
         <x:v>No</x:v>
@@ -17685,7 +17685,7 @@
         <x:v>Cambio</x:v>
       </x:c>
       <x:c r="I91" s="85" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J91" s="73" t="str">
         <x:v>No</x:v>
@@ -17775,7 +17775,7 @@
         <x:v>Lote</x:v>
       </x:c>
       <x:c r="I92" s="85" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J92" s="73" t="str">
         <x:v>No</x:v>
@@ -34752,7 +34752,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431d6b853ca84341"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1ef00c2a516429f"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -41540,7 +41540,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R502546f54d394c3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R405eceb5f81b4bad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46378,7 +46378,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60c6058681774240"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb250583aa37a44ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49072,7 +49072,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8277402dcdb84c64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R046e5d59a0524600"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51692,7 +51692,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9df49a0eef842c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R875cf3adbf7445db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55698,7 +55698,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fdb82572dc1468e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65390f8864424cb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>